--- a/tables/new/imb all/all_AP.xlsx
+++ b/tables/new/imb all/all_AP.xlsx
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3146582751203137</v>
+        <v>0.3095206059374356</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3018197393269288</v>
+        <v>0.3428104860895573</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2872766992198196</v>
+        <v>0.2885791458382526</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2610092472424145</v>
+        <v>0.3220472057224573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3106404882696876</v>
+        <v>0.2973896853541897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3168569951313866</v>
+        <v>0.3254290503694475</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3073193011283451</v>
+        <v>0.2529046919376007</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3263941021055477</v>
+        <v>0.3341689240081817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3060270606844065</v>
+        <v>0.2887712874731132</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3314185025728374</v>
+        <v>0.3280268413771049</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2522923887067756</v>
+        <v>0.2305072002454308</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3074622261688348</v>
+        <v>0.3227104133533788</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2878948621550528</v>
+        <v>0.2961640511262374</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269162893571903</v>
+        <v>0.2751671254717879</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2815140777774992</v>
+        <v>0.3093732636313103</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2443094963341608</v>
+        <v>0.2782341918218455</v>
       </c>
     </row>
     <row r="6">
@@ -843,221 +843,221 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_AP.csv</t>
+          <t>kdd_AP.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8099146175705969</v>
+        <v>0.0575777387525001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8751479347255333</v>
+        <v>0.0568344633902143</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7974663484901281</v>
+        <v>0.0585173327698281</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8390469062330571</v>
+        <v>0.0581486143387063</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8045618325634817</v>
+        <v>0.0583993712178612</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8843441953338247</v>
+        <v>0.0584555167927538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7927362920564776</v>
+        <v>0.0574556037043618</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8710799413584918</v>
+        <v>0.059956857909725</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8021247316397834</v>
+        <v>0.0586490979593633</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8645491844829815</v>
+        <v>0.0573962703332212</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7742570369998265</v>
+        <v>0.0582138372091664</v>
       </c>
       <c r="M8" t="n">
-        <v>0.882999022595065</v>
+        <v>0.0579584948185021</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8223864062932609</v>
+        <v>0.0585900232104054</v>
       </c>
       <c r="O8" t="n">
-        <v>0.844533456549876</v>
+        <v>0.0575344573935529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7897552900930537</v>
+        <v>0.0585020933402374</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8420005305157582</v>
+        <v>0.0561727622815867</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_AP.csv</t>
+          <t>synth_credit_card_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5357404212239142</v>
+        <v>0.8099146175705969</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8900586587060793</v>
+        <v>0.8751479347255333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6780855705918143</v>
+        <v>0.7974663484901281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8797364906876195</v>
+        <v>0.8390469062330571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4684283853866111</v>
+        <v>0.8045618325634817</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8780180420880421</v>
+        <v>0.8843441953338247</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3630667753399253</v>
+        <v>0.7927362920564776</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9096476507236052</v>
+        <v>0.8710799413584918</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5178564557926061</v>
+        <v>0.8021247316397834</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8920338713994076</v>
+        <v>0.8645491844829815</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3932176454966677</v>
+        <v>0.7742570369998265</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9070530651672414</v>
+        <v>0.882999022595065</v>
       </c>
       <c r="N9" t="n">
-        <v>0.635400814507469</v>
+        <v>0.8223864062932609</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8860478672220983</v>
+        <v>0.844533456549876</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6507271317956727</v>
+        <v>0.7897552900930537</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8844662316972079</v>
+        <v>0.8420005305157582</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_AP.csv</t>
+          <t>synth_mobile_money_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1759595521501368</v>
+        <v>0.5357404212239142</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2333980375553606</v>
+        <v>0.8900586587060793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2263578829242404</v>
+        <v>0.6780855705918143</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1104081998803426</v>
+        <v>0.8797364906876195</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1656572349890245</v>
+        <v>0.4684283853866111</v>
       </c>
       <c r="G10" t="n">
-        <v>0.232256205970479</v>
+        <v>0.8780180420880421</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1877575847435089</v>
+        <v>0.3630667753399253</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2299440279708058</v>
+        <v>0.9096476507236052</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2266828703369569</v>
+        <v>0.5178564557926061</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1495360732213463</v>
+        <v>0.8920338713994076</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1759004216373076</v>
+        <v>0.3932176454966677</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2453750126596796</v>
+        <v>0.9070530651672414</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2262230830214678</v>
+        <v>0.635400814507469</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1412553438354349</v>
+        <v>0.8860478672220983</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2177108685487481</v>
+        <v>0.6507271317956727</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1365418836402717</v>
+        <v>0.8844662316972079</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ulb_credit_card_fraud_label_AP.csv</t>
+          <t>telco_customer_churn_AP.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.902364634301534</v>
+        <v>0.1759595521501368</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9112509015482484</v>
+        <v>0.2333980375553606</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9158150644870352</v>
+        <v>0.2263578829242404</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9100090530298144</v>
+        <v>0.1104081998803426</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9056374327835039</v>
+        <v>0.1656572349890245</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9145152148414052</v>
+        <v>0.232256205970479</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8971078904763802</v>
+        <v>0.1877575847435089</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9085372936188266</v>
+        <v>0.2299440279708058</v>
       </c>
       <c r="J11" t="n">
-        <v>0.907513665349964</v>
+        <v>0.2266828703369569</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9131956578216772</v>
+        <v>0.1495360732213463</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8882920492980702</v>
+        <v>0.1759004216373076</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9067147977313532</v>
+        <v>0.2453750126596796</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9125233187545472</v>
+        <v>0.2262230830214678</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9143312302990924</v>
+        <v>0.1412553438354349</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9043251043222326</v>
+        <v>0.2177108685487481</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9147778049174869</v>
+        <v>0.1365418836402717</v>
       </c>
     </row>
     <row r="12">

--- a/tables/new/imb all/all_AP.xlsx
+++ b/tables/new/imb all/all_AP.xlsx
@@ -425,86 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
+          <t>Logit(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 1, 1)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD_rose</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)</t>
+          <t>XGBoost(1, 1, 0, 0)_rose</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD_rose</t>
+          <t>XGBoost(1, 1, 1, 1)_rose_BROOD</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD_rose</t>
+          <t>XGBoost(1, 1, 0, 0)_smote</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 0, 0)_rose</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)_rose</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 1, 1)_rose_BROOD</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 1, 1)_rose_BROOD</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 0, 0)_smote</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)_smote</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 0, 0)_adasyn</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>XGBoost(1, 1, 0, 0)_adasyn</t>
         </is>
@@ -513,606 +478,375 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>apata_credit_card_fraud_label_AP.csv</t>
+          <t>bank_marketing_AP.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0100300124319251</v>
+        <v>0.2646726729824488</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1776130012149707</v>
+        <v>0.2388578336697585</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0518996641433557</v>
+        <v>0.2944787937794315</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0075559267560367</v>
+        <v>0.2105493821384273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0488547546247359</v>
+        <v>0.274672588755196</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2563864322511004</v>
+        <v>0.3009502761226003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04210377028392</v>
+        <v>0.2483635420604961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1712578047017528</v>
+        <v>0.2791910672201317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0504759771195281</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.0075559267560367</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0446036955614961</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1474084937342709</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.05140724857721</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0075559267560367</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.2534711323270729</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bank_marketing_AP.csv</t>
+          <t>telco_customer_churn_AP.csv</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2510065343204352</v>
+        <v>0.2333980375553606</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2646726729824488</v>
+        <v>0.2263578829242404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2388578336697585</v>
+        <v>0.1104081998803426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2944787937794315</v>
+        <v>0.232256205970479</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2635200753905264</v>
+        <v>0.2299440279708058</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2105493821384273</v>
+        <v>0.1495360732213463</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2413609851395739</v>
+        <v>0.2453750126596796</v>
       </c>
       <c r="I3" t="n">
-        <v>0.274672588755196</v>
+        <v>0.1412553438354349</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2491027151300747</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.3009502761226003</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.2535467254096962</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.2483635420604961</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.2710009269071726</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.2791910672201317</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.252470563358688</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.2534711323270729</v>
+        <v>0.1365418836402717</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>car_insurance_fraud_label_AP.csv</t>
+          <t>kag_credit_card_approval_AP.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0873071809801524</v>
+        <v>0.0373129755082362</v>
       </c>
       <c r="C4" t="n">
-        <v>0.074275099082264</v>
+        <v>0.0527207997593884</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0676247104095683</v>
+        <v>0.0410140043687749</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06381978500045191</v>
+        <v>0.050978028299342</v>
       </c>
       <c r="F4" t="n">
-        <v>0.085119028002504</v>
+        <v>0.0720360332985291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0867222853792794</v>
+        <v>0.0289983947393249</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09432899576388019</v>
+        <v>0.0467718474881171</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0860699428710522</v>
+        <v>0.0275860435401005</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0838787707934389</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.0711328928234246</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0993479486514324</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.1109215871159596</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.08494583176634619</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0722568472705394</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.08676891932062999</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0697488362728166</v>
+        <v>0.0315884414173441</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>customer_trans_fraud_detection_label_AP.csv</t>
+          <t>vub_credit_scoring_AP.csv</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3095206059374356</v>
+        <v>0.1255747209284211</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3428104860895573</v>
+        <v>0.1289114002239812</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2885791458382526</v>
+        <v>0.1269145181818539</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3220472057224573</v>
+        <v>0.1239910608868782</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2973896853541897</v>
+        <v>0.1228994199568789</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3254290503694475</v>
+        <v>0.1290423239656195</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2529046919376007</v>
+        <v>0.1203308766522132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3341689240081817</v>
+        <v>0.1095279142536682</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2887712874731132</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.3280268413771049</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2305072002454308</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.3227104133533788</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.2961640511262374</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.2751671254717879</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.3093732636313103</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.2782341918218455</v>
+        <v>0.1259772887654006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>financial_statement_fraud_label_AP.csv</t>
+          <t>kdd_AP.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06079230372234</v>
+        <v>0.0568344633902143</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08278756815492461</v>
+        <v>0.0585173327698281</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0715528814712455</v>
+        <v>0.0581486143387063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0844320406963347</v>
+        <v>0.0584555167927538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06401744326513779</v>
+        <v>0.059956857909725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0844163830212646</v>
+        <v>0.0573962703332212</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0664252897000872</v>
+        <v>0.0579584948185021</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0955016673744768</v>
+        <v>0.0575344573935529</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0723743789553972</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.08572316427429739</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0680698731760849</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.09465064394048429</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.0744766737235359</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.0877275144176695</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0732518452232877</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0759554515508654</v>
+        <v>0.0561727622815867</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>kag_credit_card_approval_AP.csv</t>
+          <t>car_insurance_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0259387265279994</v>
+        <v>0.074275099082264</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0373129755082362</v>
+        <v>0.0676247104095683</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0527207997593884</v>
+        <v>0.06381978500045191</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0410140043687749</v>
+        <v>0.0867222853792794</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0248125214558591</v>
+        <v>0.0860699428710522</v>
       </c>
       <c r="G7" t="n">
-        <v>0.050978028299342</v>
+        <v>0.0711328928234246</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0196700029572826</v>
+        <v>0.1109215871159596</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0720360332985291</v>
+        <v>0.0722568472705394</v>
       </c>
       <c r="J7" t="n">
-        <v>0.048980821705758</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0289983947393249</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0169551535917819</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.0467718474881171</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.0414829897576883</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0275860435401005</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0438795464216541</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0315884414173441</v>
+        <v>0.0697488362728166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>kdd_AP.csv</t>
+          <t>apata_credit_card_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0575777387525001</v>
+        <v>0.1776130012149707</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0568344633902143</v>
+        <v>0.0518996641433557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0585173327698281</v>
+        <v>0.0075559267560367</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0581486143387063</v>
+        <v>0.2563864322511004</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0583993712178612</v>
+        <v>0.1712578047017528</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0584555167927538</v>
+        <v>0.0075559267560367</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0574556037043618</v>
+        <v>0.1474084937342709</v>
       </c>
       <c r="I8" t="n">
-        <v>0.059956857909725</v>
+        <v>0.0075559267560367</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0586490979593633</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0573962703332212</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.0582138372091664</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.0579584948185021</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.0585900232104054</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.0575344573935529</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.0585020933402374</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.0561727622815867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_AP.csv</t>
+          <t>financial_statement_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8099146175705969</v>
+        <v>0.08278756815492461</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8751479347255333</v>
+        <v>0.0715528814712455</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7974663484901281</v>
+        <v>0.0844320406963347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8390469062330571</v>
+        <v>0.0844163830212646</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8045618325634817</v>
+        <v>0.0955016673744768</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8843441953338247</v>
+        <v>0.08572316427429739</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7927362920564776</v>
+        <v>0.09465064394048429</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8710799413584918</v>
+        <v>0.0877275144176695</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8021247316397834</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8645491844829815</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7742570369998265</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.882999022595065</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.8223864062932609</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.844533456549876</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.7897552900930537</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.8420005305157582</v>
+        <v>0.0759554515508654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_AP.csv</t>
+          <t>customer_trans_fraud_detection_label_AP.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5357404212239142</v>
+        <v>0.3428104860895573</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8900586587060793</v>
+        <v>0.2885791458382526</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6780855705918143</v>
+        <v>0.3220472057224573</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8797364906876195</v>
+        <v>0.3254290503694475</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4684283853866111</v>
+        <v>0.3341689240081817</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8780180420880421</v>
+        <v>0.3280268413771049</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3630667753399253</v>
+        <v>0.3227104133533788</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9096476507236052</v>
+        <v>0.2751671254717879</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5178564557926061</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.8920338713994076</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.3932176454966677</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.9070530651672414</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.635400814507469</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.8860478672220983</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.6507271317956727</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.8844662316972079</v>
+        <v>0.2782341918218455</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_AP.csv</t>
+          <t>synth_mobile_money_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1759595521501368</v>
+        <v>0.8900586587060793</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2333980375553606</v>
+        <v>0.6780855705918143</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2263578829242404</v>
+        <v>0.8797364906876195</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1104081998803426</v>
+        <v>0.8780180420880421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1656572349890245</v>
+        <v>0.9096476507236052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.232256205970479</v>
+        <v>0.8920338713994076</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1877575847435089</v>
+        <v>0.9070530651672414</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2299440279708058</v>
+        <v>0.8860478672220983</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2266828703369569</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1495360732213463</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.1759004216373076</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2453750126596796</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.2262230830214678</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.1412553438354349</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.2177108685487481</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.1365418836402717</v>
+        <v>0.8844662316972079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vub_credit_scoring_AP.csv</t>
+          <t>synth_credit_card_fraud_label_AP.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1227633376388764</v>
+        <v>0.8751479347255333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1255747209284211</v>
+        <v>0.7974663484901281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1289114002239812</v>
+        <v>0.8390469062330571</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1269145181818539</v>
+        <v>0.8843441953338247</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1104019264036325</v>
+        <v>0.8710799413584918</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1239910608868782</v>
+        <v>0.8645491844829815</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1164517768393776</v>
+        <v>0.882999022595065</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1228994199568789</v>
+        <v>0.844533456549876</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1244490161689309</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.1290423239656195</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.11231502160171</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.1203308766522132</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1279840480535376</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.1095279142536682</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.127348188028461</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.1259772887654006</v>
+        <v>0.8420005305157582</v>
       </c>
     </row>
   </sheetData>
